--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H300"/>
+  <dimension ref="A1:H299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2169,49 +2169,49 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>S037</t>
+          <t>S038</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Lore</t>
+          <t>Standing rules</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Signal / Static lore</t>
+          <t>Nothing anyone owns: no brands, currencies, crypto, borrowed art or names</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Could</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>Mentioned in the shape notes; source to confirm before anything uses it</t>
+          <t>Standing rule</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Part VIII</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Claude (proposed)</t>
+          <t>Owner</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>S038</t>
+          <t>S039</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Nothing anyone owns: no brands, currencies, crypto, borrowed art or names</t>
+          <t>Photosensitivity: nothing flashes more than 3 times a second</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>Part VIII</t>
+          <t>Part XI</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
@@ -2253,17 +2253,17 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>S039</t>
+          <t>S040</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Standing rules</t>
+          <t>Audio</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Photosensitivity: nothing flashes more than 3 times a second</t>
+          <t>Vocal ad-libs and footfalls</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -2273,17 +2273,17 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>Standing rule</t>
+          <t>Owner: keep</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>Part XI</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
@@ -2293,14 +2293,46 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="n"/>
-      <c r="B41" s="6" t="n"/>
-      <c r="C41" s="6" t="n"/>
-      <c r="D41" s="6" t="n"/>
-      <c r="E41" s="6" t="n"/>
-      <c r="F41" s="6" t="n"/>
-      <c r="G41" s="6" t="n"/>
-      <c r="H41" s="6" t="n"/>
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>S041</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Audio</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>'Unveil' cue on first placement of a block type</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Won't</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Parked</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>Owner: nixed; the recipe stays unused</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -4881,16 +4913,6 @@
       <c r="F299" s="6" t="n"/>
       <c r="G299" s="6" t="n"/>
       <c r="H299" s="6" t="n"/>
-    </row>
-    <row r="300">
-      <c r="A300" s="6" t="n"/>
-      <c r="B300" s="6" t="n"/>
-      <c r="C300" s="6" t="n"/>
-      <c r="D300" s="6" t="n"/>
-      <c r="E300" s="6" t="n"/>
-      <c r="F300" s="6" t="n"/>
-      <c r="G300" s="6" t="n"/>
-      <c r="H300" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H300"/>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -890,7 +890,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Debug builds optimise hot files only</t>
+          <t>The Ctrl+F3 report tool exists (perf_report.txt); running the check awaits the owner</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
@@ -1991,12 +1991,12 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>Everything is mono today</t>
+          <t>Owner: go ahead</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Claude (proposed)</t>
+          <t>Owner</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,11 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr"/>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>Owner expected the essence attractor to do this; today it doesn't (it only draws from convergence zones). Owner to decide whether attractors should pull The Line's pivot.</t>
+        </is>
+      </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
           <t>Part XVIII</t>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -1991,12 +1991,12 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>Owner: go ahead</t>
+          <t>Owner: go ahead. Placed sounds pan, ping-pong echo, Mono audio toggle</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
@@ -2339,44 +2339,168 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="n"/>
-      <c r="B42" s="6" t="n"/>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="6" t="n"/>
-      <c r="E42" s="6" t="n"/>
-      <c r="F42" s="6" t="n"/>
-      <c r="G42" s="6" t="n"/>
-      <c r="H42" s="6" t="n"/>
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>S042</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Audio</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Footsteps on the beat, by gait and ground hardness</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>Crouch/walk/sprint; soft scuffs, hard knocks in key</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="n"/>
-      <c r="B43" s="6" t="n"/>
-      <c r="C43" s="6" t="n"/>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n"/>
-      <c r="F43" s="6" t="n"/>
-      <c r="G43" s="6" t="n"/>
-      <c r="H43" s="6" t="n"/>
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>S043</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>World</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Default plain as a fractal patchwork of three ground materials</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>Cheap per-column noise; materials swappable</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>Part II</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="n"/>
-      <c r="B44" s="6" t="n"/>
-      <c r="C44" s="6" t="n"/>
-      <c r="D44" s="6" t="n"/>
-      <c r="E44" s="6" t="n"/>
-      <c r="F44" s="6" t="n"/>
-      <c r="G44" s="6" t="n"/>
-      <c r="H44" s="6" t="n"/>
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>S044</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Buttons that look and feel pressable (mechanical press cue)</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr"/>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>Part XII</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="n"/>
-      <c r="B45" s="6" t="n"/>
-      <c r="C45" s="6" t="n"/>
-      <c r="D45" s="6" t="n"/>
-      <c r="E45" s="6" t="n"/>
-      <c r="F45" s="6" t="n"/>
-      <c r="G45" s="6" t="n"/>
-      <c r="H45" s="6" t="n"/>
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>S045</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Standing rules</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Privacy: no telemetry, crash reporting or hardware reading; target a modest old Windows PC</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>Standing rule</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -2403,12 +2403,12 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Cheap per-column noise; materials swappable</t>
+          <t>Grass / sand / pebbles by feel underfoot; flat v2; materials swappable</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -2445,10 +2445,14 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>Keys act on release; sliders are beads on a string</t>
+        </is>
+      </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
           <t>Part XII</t>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -1171,12 +1171,12 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Deliberate, low-frequency landmarks, not scatter</t>
+          <t>Glowcap, moss canopy, fern coil, sprout coil in the library</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -1335,12 +1335,12 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Deferred earlier for usage limits</t>
+          <t>Comparison rendered (A crisp / B bleed / C variation / D both); owner to pick one to build</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Comparison rendered (A crisp / B bleed / C variation / D both); owner to pick one to build</t>
+          <t>Owner picked D (bleed + variation); built into the world shader (4.16)</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -2507,14 +2507,46 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="n"/>
-      <c r="B46" s="6" t="n"/>
-      <c r="C46" s="6" t="n"/>
-      <c r="D46" s="6" t="n"/>
-      <c r="E46" s="6" t="n"/>
-      <c r="F46" s="6" t="n"/>
-      <c r="G46" s="6" t="n"/>
-      <c r="H46" s="6" t="n"/>
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>S046</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Crafting</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Crafting system brainstorm: gathering, representation, uses, advancement from the natural surroundings</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>After the playtest. Seed: microbes/germs gathered as essence, coloured/'flavoured' by the source's biological makeup. Owner to confirm priority.</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>Part XX</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Owner picked D (bleed + variation); built into the world shader (4.16)</t>
+          <t>Owner picked D; colour bleed dropped after the playtest (halo). Variation + distance filtering kept (4.16)</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -2549,34 +2549,130 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="n"/>
-      <c r="B47" s="6" t="n"/>
-      <c r="C47" s="6" t="n"/>
-      <c r="D47" s="6" t="n"/>
-      <c r="E47" s="6" t="n"/>
-      <c r="F47" s="6" t="n"/>
-      <c r="G47" s="6" t="n"/>
-      <c r="H47" s="6" t="n"/>
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>S047</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Playtest fixes</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Footsteps louder; fog haze + distance filtering; midday hitch (music slices, sliced shadow redraw)</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>From the first playtest on the owner's rig</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>4.8, 4.16, 14.7</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="n"/>
-      <c r="B48" s="6" t="n"/>
-      <c r="C48" s="6" t="n"/>
-      <c r="D48" s="6" t="n"/>
-      <c r="E48" s="6" t="n"/>
-      <c r="F48" s="6" t="n"/>
-      <c r="G48" s="6" t="n"/>
-      <c r="H48" s="6" t="n"/>
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>S048</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Forgiving power-slide timing; faster sprint (7.5)</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>Crouch/sprint in either order within 0.3-0.4 s</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="n"/>
-      <c r="B49" s="6" t="n"/>
-      <c r="C49" s="6" t="n"/>
-      <c r="D49" s="6" t="n"/>
-      <c r="E49" s="6" t="n"/>
-      <c r="F49" s="6" t="n"/>
-      <c r="G49" s="6" t="n"/>
-      <c r="H49" s="6" t="n"/>
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>S049</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Rendering</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Frame rate limit 30-200 (default 60) and vsync toggle</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>Graphics settings</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>12.y</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -2065,7 +2065,7 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>The Line prototype: travelling pivot, clockwise spin</t>
+          <t>The Line prototype: travelling pivot, clockwise spin, time expression</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -2078,7 +2078,11 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr"/>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>Playtest fixes: pivot now lands on the spot you actually spend time in x and z (16-block cells remembering where their time was spent; 30-min half-life). Expression (owner's pick): the visible sky races ahead near the line and runs slow after you leave; sun and light keep the real clock; wobble kept faint.</t>
+        </is>
+      </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
           <t>Part XVIII</t>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -2679,24 +2679,88 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="n"/>
-      <c r="B50" s="6" t="n"/>
-      <c r="C50" s="6" t="n"/>
-      <c r="D50" s="6" t="n"/>
-      <c r="E50" s="6" t="n"/>
-      <c r="F50" s="6" t="n"/>
-      <c r="G50" s="6" t="n"/>
-      <c r="H50" s="6" t="n"/>
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>S050</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Breaking blocks: how it is done, and with what tools (if any)</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>Parked</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>Owner: comes later, once we decide what tools there are. Today a click breaks a block instantly. Priority is the owner's to set.</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>Part XX</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>Claude (proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="n"/>
-      <c r="B51" s="6" t="n"/>
-      <c r="C51" s="6" t="n"/>
-      <c r="D51" s="6" t="n"/>
-      <c r="E51" s="6" t="n"/>
-      <c r="F51" s="6" t="n"/>
-      <c r="G51" s="6" t="n"/>
-      <c r="H51" s="6" t="n"/>
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>S051</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Rendering</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Pre-generated fracture: a broken block splits into pieces that tumble and settle</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>Parked</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>Owner's idea, for with S050. Cheap by design: fracture patterns baked once per shape (a handful of variants), a few short-lived pieces per break, no per-block data. Nothing flashes.</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>Part XX</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>Claude (proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -1481,7 +1481,7 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Item logistics</t>
+          <t>Item logistics: pulse through pipes</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Delivery manner undecided; owner decides after the library try-out</t>
+          <t>First slice built: harvester gathers pulse on the beat; pipes join any face and bend to meet; networks send pulse to stores/machine in turn; open ends fire it straight until a surface or a facing mouth catches it; pulses cross freely. Open: what harvesters draw from, what pulse becomes.</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Core of the factory game; shape depends on logistics</t>
+          <t>Core of the factory game. Logistics decided (pulse); waits on what pulse becomes / how it is burned</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -2763,34 +2763,130 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="n"/>
-      <c r="B52" s="6" t="n"/>
-      <c r="C52" s="6" t="n"/>
-      <c r="D52" s="6" t="n"/>
-      <c r="E52" s="6" t="n"/>
-      <c r="F52" s="6" t="n"/>
-      <c r="G52" s="6" t="n"/>
-      <c r="H52" s="6" t="n"/>
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>S052</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Translation / language packs</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>Won't</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>Owner: not a priority; English only, kept minimal so non-native speakers pick it up through play. Estimate if ever wanted: Latin scripts a few days (string table, accented glyphs); CJK needs a glyph cache.</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="n"/>
-      <c r="B53" s="6" t="n"/>
-      <c r="C53" s="6" t="n"/>
-      <c r="D53" s="6" t="n"/>
-      <c r="E53" s="6" t="n"/>
-      <c r="F53" s="6" t="n"/>
-      <c r="G53" s="6" t="n"/>
-      <c r="H53" s="6" t="n"/>
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>S053</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>A big new batch of library blocks to sort through</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>Owner isn't thrilled with the current set; wants a large pile to choose from.</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>4.13, 4.15</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="n"/>
-      <c r="B54" s="6" t="n"/>
-      <c r="C54" s="6" t="n"/>
-      <c r="D54" s="6" t="n"/>
-      <c r="E54" s="6" t="n"/>
-      <c r="F54" s="6" t="n"/>
-      <c r="G54" s="6" t="n"/>
-      <c r="H54" s="6" t="n"/>
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>S054</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Reviews: music fit; optimisation and architecture; texture library direction</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>Owner asked for a distanced look at each</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -1496,7 +1496,7 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>First slice built: harvester gathers pulse on the beat; pipes join any face and bend to meet; networks send pulse to stores/machine in turn; open ends fire it straight until a surface or a facing mouth catches it; pulses cross freely. Open: what harvesters draw from, what pulse becomes.</t>
+          <t>Built: harvester at a constant rate (faster under The Line); plain/clockwise/anticlockwise pipes give pulse spin; networks share out to stores (unlimited) and the machine; open ends fire straight, facing mouths catch; store view with bead heaps. Open: what harvesters draw from, what pulse becomes.</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
@@ -2889,64 +2889,256 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="n"/>
-      <c r="B55" s="6" t="n"/>
-      <c r="C55" s="6" t="n"/>
-      <c r="D55" s="6" t="n"/>
-      <c r="E55" s="6" t="n"/>
-      <c r="F55" s="6" t="n"/>
-      <c r="G55" s="6" t="n"/>
-      <c r="H55" s="6" t="n"/>
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>S055</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Pulse spin: three pipe kinds, spin carried and counted</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>Owner's idea; seen as corkscrew comets in the air and heaps by colour in stores</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="n"/>
-      <c r="B56" s="6" t="n"/>
-      <c r="C56" s="6" t="n"/>
-      <c r="D56" s="6" t="n"/>
-      <c r="E56" s="6" t="n"/>
-      <c r="F56" s="6" t="n"/>
-      <c r="G56" s="6" t="n"/>
-      <c r="H56" s="6" t="n"/>
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>S056</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>World</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Fliers: two-winged day-lived creatures that fly low; the line ages them</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>Owner's idea. Die after one game day or sooner under The Line; death makes grass glow vividly for a while, or grows mold on dirt/wood</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="n"/>
-      <c r="B57" s="6" t="n"/>
-      <c r="C57" s="6" t="n"/>
-      <c r="D57" s="6" t="n"/>
-      <c r="E57" s="6" t="n"/>
-      <c r="F57" s="6" t="n"/>
-      <c r="G57" s="6" t="n"/>
-      <c r="H57" s="6" t="n"/>
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>S057</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>World</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Mold that sprouts a mushroom after a game day or after rain</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>Owner's idea; rain needs a weather system (to discuss)</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>Claude (proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="n"/>
-      <c r="B58" s="6" t="n"/>
-      <c r="C58" s="6" t="n"/>
-      <c r="D58" s="6" t="n"/>
-      <c r="E58" s="6" t="n"/>
-      <c r="F58" s="6" t="n"/>
-      <c r="G58" s="6" t="n"/>
-      <c r="H58" s="6" t="n"/>
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>S058</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>World</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Covered grass turns to dirt (not overnight)</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>Deprived of sky, not of daylight</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>Part V</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="n"/>
-      <c r="B59" s="6" t="n"/>
-      <c r="C59" s="6" t="n"/>
-      <c r="D59" s="6" t="n"/>
-      <c r="E59" s="6" t="n"/>
-      <c r="F59" s="6" t="n"/>
-      <c r="G59" s="6" t="n"/>
-      <c r="H59" s="6" t="n"/>
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>S059</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>World</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Weather (rain first)</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>Owner: yet to discuss</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>Claude (proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="n"/>
-      <c r="B60" s="6" t="n"/>
-      <c r="C60" s="6" t="n"/>
-      <c r="D60" s="6" t="n"/>
-      <c r="E60" s="6" t="n"/>
-      <c r="F60" s="6" t="n"/>
-      <c r="G60" s="6" t="n"/>
-      <c r="H60" s="6" t="n"/>
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>S060</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>The Line</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>The Line grows to a plane with the player's power and influence</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Won't</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>Owner: low priority, discuss later</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>Part XVIII</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n"/>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -3141,54 +3141,210 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="n"/>
-      <c r="B61" s="6" t="n"/>
-      <c r="C61" s="6" t="n"/>
-      <c r="D61" s="6" t="n"/>
-      <c r="E61" s="6" t="n"/>
-      <c r="F61" s="6" t="n"/>
-      <c r="G61" s="6" t="n"/>
-      <c r="H61" s="6" t="n"/>
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>S061</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Diffuser: spends pulse widening The Line's band (the first loop)</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>Owner's design: feed per second keeps the band wide; harvesters above/below need it</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>6.0, XVIII</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="n"/>
-      <c r="B62" s="6" t="n"/>
-      <c r="C62" s="6" t="n"/>
-      <c r="D62" s="6" t="n"/>
-      <c r="E62" s="6" t="n"/>
-      <c r="F62" s="6" t="n"/>
-      <c r="G62" s="6" t="n"/>
-      <c r="H62" s="6" t="n"/>
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>S062</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>First-steps tutorial on a new world, skippable</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>One line at a time, moves on as done; Enter skips</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="6" t="n"/>
-      <c r="B63" s="6" t="n"/>
-      <c r="C63" s="6" t="n"/>
-      <c r="D63" s="6" t="n"/>
-      <c r="E63" s="6" t="n"/>
-      <c r="F63" s="6" t="n"/>
-      <c r="G63" s="6" t="n"/>
-      <c r="H63" s="6" t="n"/>
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>S063</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>New world starts with harvester, pipe, chest, diffuser on the hotbar</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr"/>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="n"/>
-      <c r="B64" s="6" t="n"/>
-      <c r="C64" s="6" t="n"/>
-      <c r="D64" s="6" t="n"/>
-      <c r="E64" s="6" t="n"/>
-      <c r="F64" s="6" t="n"/>
-      <c r="G64" s="6" t="n"/>
-      <c r="H64" s="6" t="n"/>
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>S064</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Colour-vision modes, one per kind of colour blindness</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>Owner: red vs blue (pulse spin) must stay unmistakable for each kind. Spin already has non-colour cues (swirl, thread hand, bead turn, corkscrew)</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>11.x</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="n"/>
-      <c r="B65" s="6" t="n"/>
-      <c r="C65" s="6" t="n"/>
-      <c r="D65" s="6" t="n"/>
-      <c r="E65" s="6" t="n"/>
-      <c r="F65" s="6" t="n"/>
-      <c r="G65" s="6" t="n"/>
-      <c r="H65" s="6" t="n"/>
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>S065</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Machines sped up or slowed by time flux</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>Owner: pipes and pulse in the air stay unaffected; harvesters are the first</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n"/>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -2869,12 +2869,12 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>Owner asked for a distanced look at each</t>
+          <t>docs/REVIEW_2026-09.md; perf fixes merged, proposals await the owner</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -2953,7 +2953,7 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Part XXI</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -2827,12 +2827,12 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>Owner isn't thrilled with the current set; wants a large pile to choose from.</t>
+          <t>36 trial materials in the library (batch_sept.vtex), four families; waiting on the owner's sort</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -3285,12 +3285,12 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>Owner: red vs blue (pulse spin) must stay unmistakable for each kind. Spin already has non-colour cues (swirl, thread hand, bead turn, corkscrew)</t>
+          <t>Accessibility &gt; Colour vision: 5 modes for the pulse colours; tested with dichromat simulations (the big win: no-colour, where blue and red merged)</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -725,12 +725,12 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>Owner-requested for the first test; the owner sets Must</t>
+          <t>Owner-requested for the first test; the owner sets Must; First build: compiles clean, awaiting the owner's run</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Owner-requested for the first test; the owner sets Must</t>
+          <t>Owner-requested for the first test; the owner sets Must; First build: compiles clean, awaiting the owner's run</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Draft in prototypes/terrain_draft; Owner-requested for the first test; the owner sets Must</t>
+          <t>Draft in prototypes/terrain_draft; Owner-requested for the first test; the owner sets Must; First build: compiles clean, awaiting the owner's run</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Owner-requested for the first test; the owner sets Must</t>
+          <t>Owner-requested for the first test; the owner sets Must; First build: compiles clean, awaiting the owner's run</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
@@ -935,12 +935,12 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Owner-requested for the first test; the owner sets Must</t>
+          <t>Owner-requested for the first test; the owner sets Must; First build: compiles clean, awaiting the owner's run</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>DESIGN 7</t>
+          <t>DESIGN 9</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>Owner-requested for the first test; the owner sets Must</t>
+          <t>Owner-requested for the first test; the owner sets Must; First build: compiles clean, awaiting the owner's run</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Owner-requested for the first test; the owner sets Must</t>
+          <t>Owner-requested for the first test; the owner sets Must; First build: compiles clean, awaiting the owner's run</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>Owner-requested for the first test; the owner sets Must</t>
+          <t>Owner-requested for the first test; the owner sets Must; First build: compiles clean, awaiting the owner's run</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -1355,12 +1355,12 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Owner-requested for the first test; the owner sets Must</t>
+          <t>Owner-requested for the first test; the owner sets Must; First build: compiles clean, awaiting the owner's run</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -1397,12 +1397,12 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>Owner-requested for the first test; the owner sets Must</t>
+          <t>Owner-requested for the first test; the owner sets Must; First build: compiles clean, awaiting the owner's run</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>DESIGN 7</t>
+          <t>DESIGN 9</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>DESIGN 7</t>
+          <t>DESIGN 9</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>DESIGN 6</t>
+          <t>DESIGN 7</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>DESIGN 6</t>
+          <t>DESIGN 7</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>DESIGN 5</t>
+          <t>DESIGN 6</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>DESIGN 5</t>
+          <t>DESIGN 6</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>DESIGN 5</t>
+          <t>DESIGN 6</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
@@ -2173,74 +2173,298 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="n"/>
-      <c r="B37" s="6" t="n"/>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="6" t="n"/>
-      <c r="G37" s="6" t="n"/>
-      <c r="H37" s="6" t="n"/>
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>S036</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>World</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Cheap volumetric ground fog</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>Owner idea; priority for the owner</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>DESIGN 5</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="n"/>
-      <c r="B38" s="6" t="n"/>
-      <c r="C38" s="6" t="n"/>
-      <c r="D38" s="6" t="n"/>
-      <c r="E38" s="6" t="n"/>
-      <c r="F38" s="6" t="n"/>
-      <c r="G38" s="6" t="n"/>
-      <c r="H38" s="6" t="n"/>
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>S037</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>World</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Wind fog: drifting mist and dust</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>Owner idea; priority for the owner</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>DESIGN 5</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="n"/>
-      <c r="B39" s="6" t="n"/>
-      <c r="C39" s="6" t="n"/>
-      <c r="D39" s="6" t="n"/>
-      <c r="E39" s="6" t="n"/>
-      <c r="F39" s="6" t="n"/>
-      <c r="G39" s="6" t="n"/>
-      <c r="H39" s="6" t="n"/>
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>S038</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>World</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Precipitation in varying degrees</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>Owner idea; priority for the owner</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>DESIGN 5</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="n"/>
-      <c r="B40" s="6" t="n"/>
-      <c r="C40" s="6" t="n"/>
-      <c r="D40" s="6" t="n"/>
-      <c r="E40" s="6" t="n"/>
-      <c r="F40" s="6" t="n"/>
-      <c r="G40" s="6" t="n"/>
-      <c r="H40" s="6" t="n"/>
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>S039</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>World</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Cloud cover casting shadows (and cutting solar charge)</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>Owner idea; the charge link is proposed</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>DESIGN 5</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="n"/>
-      <c r="B41" s="6" t="n"/>
-      <c r="C41" s="6" t="n"/>
-      <c r="D41" s="6" t="n"/>
-      <c r="E41" s="6" t="n"/>
-      <c r="F41" s="6" t="n"/>
-      <c r="G41" s="6" t="n"/>
-      <c r="H41" s="6" t="n"/>
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>S040</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Mech</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Quartz crusher: energy from quartz the mech unearths (sun-charged crystals, or alongside solar)</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>Owner idea; which option, and when, is the owner's call</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>DESIGN 4</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="n"/>
-      <c r="B42" s="6" t="n"/>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="6" t="n"/>
-      <c r="E42" s="6" t="n"/>
-      <c r="F42" s="6" t="n"/>
-      <c r="G42" s="6" t="n"/>
-      <c r="H42" s="6" t="n"/>
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>S041</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Terrain</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Coal veins that can catch fire and smoulder, destroying the coal</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>Owner idea; priority for the owner</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>DESIGN 3</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="n"/>
-      <c r="B43" s="6" t="n"/>
-      <c r="C43" s="6" t="n"/>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n"/>
-      <c r="F43" s="6" t="n"/>
-      <c r="G43" s="6" t="n"/>
-      <c r="H43" s="6" t="n"/>
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>S042</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Item entities and projectiles from capped, fixed-size pools (merge, fade, recycle)</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>Owner: allowed if governed; needed for rockets in the first test</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>DESIGN 3</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -1103,12 +1103,12 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Owner-requested for the first test; the owner sets Must</t>
+          <t>Owner-requested for the first test; the owner sets Must; Prototype build: tested natively and cross-compiles clean, awaiting the owner's run</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>Owner-requested for the first test; the owner sets Must</t>
+          <t>Owner-requested for the first test; the owner sets Must; Prototype build: tested natively and cross-compiles clean, awaiting the owner's run</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Scale reads through it</t>
+          <t>Scale reads through it; Built: walking through trees and bushes knocks them down; Prototype build: tested natively and cross-compiles clean, awaiting the owner's run</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Owner-requested for the first test; the owner sets Must</t>
+          <t>Owner-requested for the first test; the owner sets Must; Prototype build: tested natively and cross-compiles clean, awaiting the owner's run</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>Owner-requested for the first test; the owner sets Must</t>
+          <t>Owner-requested for the first test; the owner sets Must; Prototype build: tested natively and cross-compiles clean, awaiting the owner's run</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -1523,12 +1523,12 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Owner-requested for the first test; the owner sets Must</t>
+          <t>Owner-requested for the first test; the owner sets Must; Prototype build: tested natively and cross-compiles clean, awaiting the owner's run</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Owner-requested for the first test; the owner sets Must</t>
+          <t>Owner-requested for the first test; the owner sets Must; Prototype build: tested natively and cross-compiles clean, awaiting the owner's run</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Owner-requested for the first test; the owner sets Must</t>
+          <t>Owner-requested for the first test; the owner sets Must; Reticle per weapon, seeker ring, lock brackets and energy/sun/health bands built; Prototype build: tested natively and cross-compiles clean, awaiting the owner's run</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>Owner-requested for the first test; the owner sets Must. Budgeted spread rule on a sparse set (LG2's idea, re-implemented safely)</t>
+          <t>Owner-requested for the first test; the owner sets Must. Budgeted spread rule on a sparse set (LG2's idea, re-implemented safely); Prototype build: tested natively and cross-compiles clean, awaiting the owner's run</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>Tuning aids</t>
+          <t>Tuning aids; R resets the field, T skips an hour; outside view and infinite energy still to do</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Owner: allowed if governed; needed for rockets in the first test</t>
+          <t>Owner: allowed if governed; needed for rockets in the first test; Pools built: rockets 48, tracers 96, debris 1024, plates 64, fire 600 cells, events 4096; Prototype build: tested natively and cross-compiles clean, awaiting the owner's run</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -2467,14 +2467,46 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="n"/>
-      <c r="B44" s="6" t="n"/>
-      <c r="C44" s="6" t="n"/>
-      <c r="D44" s="6" t="n"/>
-      <c r="E44" s="6" t="n"/>
-      <c r="F44" s="6" t="n"/>
-      <c r="G44" s="6" t="n"/>
-      <c r="H44" s="6" t="n"/>
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>S043</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Weapons</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>The wanderer sheds armour plates as it is hurt; the mech collects them by walking over them (not used yet)</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>Owner-requested; the owner sets Must; Prototype build: tested natively and cross-compiles clean, awaiting the owner's run</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>DESIGN 3</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
